--- a/diseases/d018/2020-2025.xlsx
+++ b/diseases/d018/2020-2025.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>19</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0.03663817267769401</v>
       </c>
@@ -1949,9 +1946,6 @@
       <c r="O10" t="n">
         <v>10</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.01928324877773369</v>
       </c>
@@ -2837,9 +2831,6 @@
       <c r="O16" t="n">
         <v>8</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0.01542659902218695</v>
       </c>
@@ -3725,9 +3716,6 @@
       <c r="O22" t="n">
         <v>8</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0.01542659902218695</v>
       </c>
@@ -4761,9 +4749,6 @@
       <c r="O29" t="n">
         <v>13</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0.02506822341105379</v>
       </c>
@@ -5649,9 +5634,6 @@
       <c r="O35" t="n">
         <v>20</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0.03856649755546737</v>
       </c>
@@ -6537,9 +6519,6 @@
       <c r="O41" t="n">
         <v>20</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0.03856649755546737</v>
       </c>
@@ -7573,9 +7552,6 @@
       <c r="O48" t="n">
         <v>20</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0.03856649755546737</v>
       </c>
@@ -8461,9 +8437,6 @@
       <c r="O54" t="n">
         <v>19</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0.03663817267769401</v>
       </c>
@@ -9349,9 +9322,6 @@
       <c r="O60" t="n">
         <v>41</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.07906131998870811</v>
       </c>
@@ -10385,9 +10355,6 @@
       <c r="O67" t="n">
         <v>60</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0.1156994926664021</v>
       </c>
@@ -11273,9 +11240,6 @@
       <c r="O73" t="n">
         <v>32</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0.06170639608874779</v>
       </c>
@@ -12309,9 +12273,6 @@
       <c r="O80" t="n">
         <v>20</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.03857399835742271</v>
       </c>
@@ -13197,9 +13158,6 @@
       <c r="O86" t="n">
         <v>8</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.01542959934296909</v>
       </c>
@@ -14085,9 +14043,6 @@
       <c r="O92" t="n">
         <v>14</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0.0270017988501959</v>
       </c>
@@ -14973,9 +14928,6 @@
       <c r="O98" t="n">
         <v>21</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0.04050269827529385</v>
       </c>
@@ -16009,9 +15961,6 @@
       <c r="O105" t="n">
         <v>20</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0.03857399835742271</v>
       </c>
@@ -16897,9 +16846,6 @@
       <c r="O111" t="n">
         <v>30</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0.05786099753613407</v>
       </c>
@@ -17785,9 +17731,6 @@
       <c r="O117" t="n">
         <v>19</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0.03664529843955158</v>
       </c>
@@ -18821,9 +18764,6 @@
       <c r="O124" t="n">
         <v>18</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0.03471659852168044</v>
       </c>
@@ -19709,9 +19649,6 @@
       <c r="O130" t="n">
         <v>15</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0.02893049876806704</v>
       </c>
@@ -20745,9 +20682,6 @@
       <c r="O137" t="n">
         <v>35</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0.06750449712548975</v>
       </c>
@@ -21633,9 +21567,6 @@
       <c r="O143" t="n">
         <v>79</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0.1523672935118197</v>
       </c>
@@ -22521,9 +22452,6 @@
       <c r="O149" t="n">
         <v>31</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0.0597896974540052</v>
       </c>
@@ -23557,9 +23485,6 @@
       <c r="O156" t="n">
         <v>14</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0.02703615486089353</v>
       </c>
@@ -24445,9 +24370,6 @@
       <c r="O162" t="n">
         <v>8</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>0.01544923134908202</v>
       </c>
@@ -25333,9 +25255,6 @@
       <c r="O168" t="n">
         <v>5</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0.00965576959317626</v>
       </c>
@@ -26369,9 +26288,6 @@
       <c r="O175" t="n">
         <v>5</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="R175" t="n">
         <v>0.00965576959317626</v>
       </c>
@@ -27257,9 +27173,6 @@
       <c r="O181" t="n">
         <v>15</v>
       </c>
-      <c r="Q181" t="n">
-        <v>0</v>
-      </c>
       <c r="R181" t="n">
         <v>0.02896730877952878</v>
       </c>
@@ -28145,9 +28058,6 @@
       <c r="O187" t="n">
         <v>24</v>
       </c>
-      <c r="Q187" t="n">
-        <v>0</v>
-      </c>
       <c r="R187" t="n">
         <v>0.04634769404724604</v>
       </c>
@@ -29181,9 +29091,6 @@
       <c r="O194" t="n">
         <v>31</v>
       </c>
-      <c r="Q194" t="n">
-        <v>0</v>
-      </c>
       <c r="R194" t="n">
         <v>0.05986577147769281</v>
       </c>
@@ -30069,9 +29976,6 @@
       <c r="O200" t="n">
         <v>12</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>0.02317384702362302</v>
       </c>
@@ -30957,9 +30861,6 @@
       <c r="O206" t="n">
         <v>17</v>
       </c>
-      <c r="Q206" t="n">
-        <v>0</v>
-      </c>
       <c r="R206" t="n">
         <v>0.03282961661679928</v>
       </c>
@@ -31993,9 +31894,6 @@
       <c r="O213" t="n">
         <v>35</v>
       </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
       <c r="R213" t="n">
         <v>0.06759038715223382</v>
       </c>
@@ -32881,9 +32779,6 @@
       <c r="O219" t="n">
         <v>104</v>
       </c>
-      <c r="Q219" t="n">
-        <v>0</v>
-      </c>
       <c r="R219" t="n">
         <v>0.2008400075380662</v>
       </c>
@@ -33769,9 +33664,6 @@
       <c r="O225" t="n">
         <v>32</v>
       </c>
-      <c r="Q225" t="n">
-        <v>0</v>
-      </c>
       <c r="R225" t="n">
         <v>0.06179692539632806</v>
       </c>
@@ -34805,9 +34697,6 @@
       <c r="O232" t="n">
         <v>20</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="R232" t="n">
         <v>0.03864828474371134</v>
       </c>
@@ -35693,9 +35582,6 @@
       <c r="O238" t="n">
         <v>8</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="R238" t="n">
         <v>0.01545931389748454</v>
       </c>
@@ -36581,9 +36467,6 @@
       <c r="O244" t="n">
         <v>14</v>
       </c>
-      <c r="Q244" t="n">
-        <v>0</v>
-      </c>
       <c r="R244" t="n">
         <v>0.02705379932059794</v>
       </c>
@@ -37617,9 +37500,6 @@
       <c r="O251" t="n">
         <v>13</v>
       </c>
-      <c r="Q251" t="n">
-        <v>0</v>
-      </c>
       <c r="R251" t="n">
         <v>0.02512138508341237</v>
       </c>
@@ -38505,9 +38385,6 @@
       <c r="O257" t="n">
         <v>30</v>
       </c>
-      <c r="Q257" t="n">
-        <v>0</v>
-      </c>
       <c r="R257" t="n">
         <v>0.05797242711556701</v>
       </c>
@@ -39393,9 +39270,6 @@
       <c r="O263" t="n">
         <v>28</v>
       </c>
-      <c r="Q263" t="n">
-        <v>0</v>
-      </c>
       <c r="R263" t="n">
         <v>0.05410759864119587</v>
       </c>
@@ -40429,9 +40303,6 @@
       <c r="O270" t="n">
         <v>45</v>
       </c>
-      <c r="Q270" t="n">
-        <v>0</v>
-      </c>
       <c r="R270" t="n">
         <v>0.08695864067335052</v>
       </c>
@@ -41317,9 +41188,6 @@
       <c r="O276" t="n">
         <v>31</v>
       </c>
-      <c r="Q276" t="n">
-        <v>0</v>
-      </c>
       <c r="R276" t="n">
         <v>0.05990484135275257</v>
       </c>
@@ -42353,9 +42221,6 @@
       <c r="O283" t="n">
         <v>36</v>
       </c>
-      <c r="Q283" t="n">
-        <v>0</v>
-      </c>
       <c r="R283" t="n">
         <v>0.06956691253868041</v>
       </c>
@@ -43241,9 +43106,6 @@
       <c r="O289" t="n">
         <v>72</v>
       </c>
-      <c r="Q289" t="n">
-        <v>0</v>
-      </c>
       <c r="R289" t="n">
         <v>0.1391338250773608</v>
       </c>
@@ -44129,9 +43991,6 @@
       <c r="O295" t="n">
         <v>125</v>
       </c>
-      <c r="Q295" t="n">
-        <v>0</v>
-      </c>
       <c r="R295" t="n">
         <v>0.2415517796481959</v>
       </c>
@@ -45165,9 +45024,6 @@
       <c r="O302" t="n">
         <v>30</v>
       </c>
-      <c r="Q302" t="n">
-        <v>0</v>
-      </c>
       <c r="R302" t="n">
         <v>0.05797242711556701</v>
       </c>
@@ -46053,9 +45909,6 @@
       <c r="O308" t="n">
         <v>19</v>
       </c>
-      <c r="Q308" t="n">
-        <v>0</v>
-      </c>
       <c r="R308" t="n">
         <v>0.03673798411720268</v>
       </c>
@@ -46941,9 +46794,6 @@
       <c r="O314" t="n">
         <v>13</v>
       </c>
-      <c r="Q314" t="n">
-        <v>0</v>
-      </c>
       <c r="R314" t="n">
         <v>0.02513651544861236</v>
       </c>
@@ -47977,9 +47827,6 @@
       <c r="O321" t="n">
         <v>10</v>
       </c>
-      <c r="Q321" t="n">
-        <v>0</v>
-      </c>
       <c r="R321" t="n">
         <v>0.0193357811143172</v>
       </c>
@@ -48865,9 +48712,6 @@
       <c r="O327" t="n">
         <v>22</v>
       </c>
-      <c r="Q327" t="n">
-        <v>0</v>
-      </c>
       <c r="R327" t="n">
         <v>0.04253871845149784</v>
       </c>
@@ -49753,9 +49597,6 @@
       <c r="O333" t="n">
         <v>30</v>
       </c>
-      <c r="Q333" t="n">
-        <v>0</v>
-      </c>
       <c r="R333" t="n">
         <v>0.05800734334295159</v>
       </c>
@@ -50789,9 +50630,6 @@
       <c r="O340" t="n">
         <v>27</v>
       </c>
-      <c r="Q340" t="n">
-        <v>0</v>
-      </c>
       <c r="R340" t="n">
         <v>0.05220660900865644</v>
       </c>
@@ -51677,9 +51515,6 @@
       <c r="O346" t="n">
         <v>25</v>
       </c>
-      <c r="Q346" t="n">
-        <v>0</v>
-      </c>
       <c r="R346" t="n">
         <v>0.048339452785793</v>
       </c>
@@ -52565,9 +52400,6 @@
       <c r="O352" t="n">
         <v>28</v>
       </c>
-      <c r="Q352" t="n">
-        <v>0</v>
-      </c>
       <c r="R352" t="n">
         <v>0.05414018712008815</v>
       </c>
@@ -53601,9 +53433,6 @@
       <c r="O359" t="n">
         <v>21</v>
       </c>
-      <c r="Q359" t="n">
-        <v>0</v>
-      </c>
       <c r="R359" t="n">
         <v>0.04060514034006612</v>
       </c>
@@ -54489,9 +54318,6 @@
       <c r="O365" t="n">
         <v>53</v>
       </c>
-      <c r="Q365" t="n">
-        <v>0</v>
-      </c>
       <c r="R365" t="n">
         <v>0.1024796399058811</v>
       </c>
@@ -55525,9 +55351,6 @@
       <c r="O372" t="n">
         <v>70</v>
       </c>
-      <c r="Q372" t="n">
-        <v>0</v>
-      </c>
       <c r="R372" t="n">
         <v>0.1353504678002204</v>
       </c>
@@ -56413,9 +56236,6 @@
       <c r="O378" t="n">
         <v>55</v>
       </c>
-      <c r="Q378" t="n">
-        <v>0</v>
-      </c>
       <c r="R378" t="n">
         <v>0.1063467961287446</v>
       </c>
@@ -57301,9 +57121,6 @@
       <c r="O384" t="n">
         <v>12</v>
       </c>
-      <c r="Q384" t="n">
-        <v>0</v>
-      </c>
       <c r="R384" t="n">
         <v>0.02322564334765946</v>
       </c>
@@ -58337,9 +58154,6 @@
       <c r="O391" t="n">
         <v>14</v>
       </c>
-      <c r="Q391" t="n">
-        <v>0</v>
-      </c>
       <c r="R391" t="n">
         <v>0.0270965839056027</v>
       </c>
@@ -59225,9 +59039,6 @@
       <c r="O397" t="n">
         <v>11</v>
       </c>
-      <c r="Q397" t="n">
-        <v>0</v>
-      </c>
       <c r="R397" t="n">
         <v>0.02129017306868784</v>
       </c>
@@ -60113,9 +59924,6 @@
       <c r="O403" t="n">
         <v>8</v>
       </c>
-      <c r="Q403" t="n">
-        <v>0</v>
-      </c>
       <c r="R403" t="n">
         <v>0.01548376223177297</v>
       </c>
@@ -61001,9 +60809,6 @@
       <c r="O409" t="n">
         <v>18</v>
       </c>
-      <c r="Q409" t="n">
-        <v>0</v>
-      </c>
       <c r="R409" t="n">
         <v>0.03483846502148918</v>
       </c>
@@ -62037,9 +61842,6 @@
       <c r="O416" t="n">
         <v>25</v>
       </c>
-      <c r="Q416" t="n">
-        <v>0</v>
-      </c>
       <c r="R416" t="n">
         <v>0.04838675697429054</v>
       </c>
@@ -62925,9 +62727,6 @@
       <c r="O422" t="n">
         <v>11</v>
       </c>
-      <c r="Q422" t="n">
-        <v>0</v>
-      </c>
       <c r="R422" t="n">
         <v>0.02129017306868784</v>
       </c>
@@ -63961,9 +63760,6 @@
       <c r="O429" t="n">
         <v>15</v>
       </c>
-      <c r="Q429" t="n">
-        <v>0</v>
-      </c>
       <c r="R429" t="n">
         <v>0.02903205418457432</v>
       </c>
@@ -64849,9 +64645,6 @@
       <c r="O435" t="n">
         <v>16</v>
       </c>
-      <c r="Q435" t="n">
-        <v>0</v>
-      </c>
       <c r="R435" t="n">
         <v>0.03096752446354594</v>
       </c>
@@ -65737,9 +65530,6 @@
       <c r="O441" t="n">
         <v>27</v>
       </c>
-      <c r="Q441" t="n">
-        <v>0</v>
-      </c>
       <c r="R441" t="n">
         <v>0.05225769753223378</v>
       </c>
@@ -66773,9 +66563,6 @@
       <c r="O448" t="n">
         <v>47</v>
       </c>
-      <c r="Q448" t="n">
-        <v>0</v>
-      </c>
       <c r="R448" t="n">
         <v>0.09096710311166621</v>
       </c>
@@ -67660,9 +67447,6 @@
       </c>
       <c r="O454" t="n">
         <v>26</v>
-      </c>
-      <c r="Q454" t="n">
-        <v>0</v>
       </c>
       <c r="R454" t="n">
         <v>0.05032222725326217</v>
